--- a/results/DR_results/01_pollution_assessment/SumRel_Focus/tables/varpart_summary.xlsx
+++ b/results/DR_results/01_pollution_assessment/SumRel_Focus/tables/varpart_summary.xlsx
@@ -470,25 +470,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.2031441494926817</v>
+        <v>0.2238407198539597</v>
       </c>
       <c r="C2" t="n">
-        <v>0.0856142278450287</v>
+        <v>0.08174763095836679</v>
       </c>
       <c r="D2" t="n">
-        <v>0.2639405444407348</v>
+        <v>0.302303127457364</v>
       </c>
       <c r="E2" t="n">
-        <v>0.1783263165957061</v>
+        <v>0.2205554964989972</v>
       </c>
       <c r="F2" t="n">
-        <v>0.02481783289697559</v>
+        <v>0.003285223354962508</v>
       </c>
       <c r="G2" t="n">
-        <v>0.06079639494805311</v>
+        <v>0.07846240760340428</v>
       </c>
       <c r="H2" t="n">
-        <v>0.7360594555592652</v>
+        <v>0.697696872542636</v>
       </c>
     </row>
   </sheetData>
